--- a/review/abilities/workbooks/29_Class_Warden.xlsx
+++ b/review/abilities/workbooks/29_Class_Warden.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Level 1'!$A$4:$M$7</definedName>
@@ -27,9 +27,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'All Signatures'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Power Watchlist'!$A$4:$J$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Power Watchlist'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -206,7 +206,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -243,19 +243,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1392,15 +1379,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1718,15 +1702,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2048,15 +2029,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2728,15 +2706,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3300,15 +3275,12 @@
       <formula>H5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>H5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>H5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3332,7 +3304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3347,12 +3319,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="12" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="12" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3433,30 +3404,25 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3480,7 +3446,6 @@
       <c r="O5" s="8" t="inlineStr"/>
       <c r="P5" s="8" t="inlineStr"/>
       <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="9" t="inlineStr"/>
@@ -3500,7 +3465,6 @@
       <c r="O6" s="9" t="inlineStr"/>
       <c r="P6" s="9" t="inlineStr"/>
       <c r="Q6" s="9" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="8" t="inlineStr"/>
@@ -3520,7 +3484,6 @@
       <c r="O7" s="8" t="inlineStr"/>
       <c r="P7" s="8" t="inlineStr"/>
       <c r="Q7" s="8" t="inlineStr"/>
-      <c r="R7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="9" t="inlineStr"/>
@@ -3540,7 +3503,6 @@
       <c r="O8" s="9" t="inlineStr"/>
       <c r="P8" s="9" t="inlineStr"/>
       <c r="Q8" s="9" t="inlineStr"/>
-      <c r="R8" s="9" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="8" t="inlineStr"/>
@@ -3560,7 +3522,6 @@
       <c r="O9" s="8" t="inlineStr"/>
       <c r="P9" s="8" t="inlineStr"/>
       <c r="Q9" s="8" t="inlineStr"/>
-      <c r="R9" s="8" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="9" t="inlineStr"/>
@@ -3580,7 +3541,6 @@
       <c r="O10" s="9" t="inlineStr"/>
       <c r="P10" s="9" t="inlineStr"/>
       <c r="Q10" s="9" t="inlineStr"/>
-      <c r="R10" s="9" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="8" t="inlineStr"/>
@@ -3600,7 +3560,6 @@
       <c r="O11" s="8" t="inlineStr"/>
       <c r="P11" s="8" t="inlineStr"/>
       <c r="Q11" s="8" t="inlineStr"/>
-      <c r="R11" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="9" t="inlineStr"/>
@@ -3620,7 +3579,6 @@
       <c r="O12" s="9" t="inlineStr"/>
       <c r="P12" s="9" t="inlineStr"/>
       <c r="Q12" s="9" t="inlineStr"/>
-      <c r="R12" s="9" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="8" t="inlineStr"/>
@@ -3640,7 +3598,6 @@
       <c r="O13" s="8" t="inlineStr"/>
       <c r="P13" s="8" t="inlineStr"/>
       <c r="Q13" s="8" t="inlineStr"/>
-      <c r="R13" s="8" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="9" t="inlineStr"/>
@@ -3660,7 +3617,6 @@
       <c r="O14" s="9" t="inlineStr"/>
       <c r="P14" s="9" t="inlineStr"/>
       <c r="Q14" s="9" t="inlineStr"/>
-      <c r="R14" s="9" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="8" t="inlineStr"/>
@@ -3680,7 +3636,6 @@
       <c r="O15" s="8" t="inlineStr"/>
       <c r="P15" s="8" t="inlineStr"/>
       <c r="Q15" s="8" t="inlineStr"/>
-      <c r="R15" s="8" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="9" t="inlineStr"/>
@@ -3700,23 +3655,19 @@
       <c r="O16" s="9" t="inlineStr"/>
       <c r="P16" s="9" t="inlineStr"/>
       <c r="Q16" s="9" t="inlineStr"/>
-      <c r="R16" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>

--- a/review/abilities/workbooks/29_Class_Warden.xlsx
+++ b/review/abilities/workbooks/29_Class_Warden.xlsx
@@ -751,17 +751,24 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Level 1: Aim, speak with beasts, or twin-strike.</t>
+        </is>
+      </c>
+    </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Design read</t>
+          <t>• Level 3: Volley, entangle, or conjure a green spear.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Wilderness hunter and guide. Signatures track, move allies through terrain, identify quarry and make one Knowledge-based attack. The class has a strong exploration identity and a clear party role.</t>
+          <t>• Level 7: Mark the quarry, call a beast, or finish the hunt from the blind spot.</t>
         </is>
       </c>
     </row>
@@ -775,7 +782,7 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Excellent exploration and group mobility; Turn the Hunt is a solid Knowledge attack; Know What You Hunt is a strong support capstone. The class feels like a guide rather than a generic ranger.</t>
+          <t>Wilderness hunter and guide. Marksman, Wildcaller and Stalker; the class reads the land and closes the hunt.</t>
         </is>
       </c>
     </row>
@@ -789,7 +796,7 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>A Watchful Rest is a very strong 8-hour buff for a 10-minute action; Know What You Hunt overlaps Intellect Expose the Mechanism. The class file lacks the standard 'Signature identity in play' section.</t>
+          <t>Clear three-way ranger split. Strong ranged, nature control and melee pursuit.</t>
         </is>
       </c>
     </row>
@@ -803,7 +810,7 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Add the missing class section. Playtest A Watchful Rest; limit it to one watch or require the Warden to stay awake. Differentiate Know What You Hunt from the Intellect card by duration and scope.</t>
+          <t>Mark the Quarry's day-long 2 Boons is campaign-scale. Death from the Blind Spot is a full-turn commit. Watch the called beast's CV and DA control.</t>
         </is>
       </c>
     </row>
@@ -817,7 +824,7 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Playtest the day-long mark, the commanded beast, and the full-turn blind-spot strike.</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -896,10 +903,17 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Steady Aim; Beast Speech; Twin Strike</t>
+        </is>
+      </c>
+    </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Findings to decide</t>
+          <t>Volley; Entangling Growth; The Green Spear</t>
         </is>
       </c>
     </row>
@@ -911,7 +925,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Mark the Quarry; Call the Wild; Death from the Blind Spot</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -988,6 +1002,13 @@
       <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Differentiate by time and scope: Intellect reads the immediate scene; Warden knows the quarry over a hunt. Make the Master investigation (Test the Hypothesis) clearly bigger than the one-minute version. State the intended overlap in the class guidance if it is deliberate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Redesign supersedes the earlier power-spike finding; re-check after playtest.</t>
         </is>
       </c>
     </row>
@@ -1036,8 +1057,8 @@
   </sheetData>
   <mergeCells count="28">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="B8:D8"/>
@@ -1188,12 +1209,12 @@
     <row r="5" ht="79" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Follow My Footsteps</t>
+          <t>Steady Aim</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>signature-warden-follow-my-footsteps</t>
+          <t>signature-warden-keep-the-quarry-close</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1203,115 +1224,131 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Self and one adjacent willing ally able to move.</t>
+          <t>Self; one visible creature.</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Move up to 1 square, then the ally may move up to 1 square. Both movements ignore difficult-terrain surcharges and do not provoke. Each must follow a legal route and end in a separate supported free square. This does not cross gaps or standing creatures. The ally spends no action.</t>
+          <t>Aim at one visible creature. Until you move, you gain 1 Boon to all attacks you make against that creature and ignore partial cover from it.</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Move up to 1 square, then the ally may move up to 1 square. Both movements ignore difficult-terrain surcharges and do not provoke. Each must follow a legal route and end in a separate supported free square. This does not cross gaps or standing creatures. The ally spends no action.</t>
+          <t>Aim at one visible creature. Until you move, you gain 1 Boon to all attacks you make against that creature and ignore partial cover from it.</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Self and an ally move 1 ignoring difficult terrain; modest level-1 mobility.</t>
+          <t>Marksman: aim once; all attacks against that creature gain 1 Boon and ignore partial cover until you move.</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the ally must remain adjacent throughout and whether it can move through the Warden's square.</t>
+          <t>Approved: Maneuver. Aim at one creature; until you move, all attacks against it gain 1 Boon and ignore partial cover.</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="79" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Keep the Quarry Close</t>
+          <t>Beast Speech</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>signature-warden-keep-the-quarry-close</t>
+          <t>signature-warden-read-the-passing</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Self, after your Main Action attack against one visible creature.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Once on your turn, after resolving a Standard or Strong Main Action attack, move toward one creature affected by it: up to 1 square on Standard, or 2 on Strong. This movement does not provoke. You must be able to move and follow a legal route; it grants no attack.</t>
+          <t>For the scene, you can speak with animals. You can ask questions and understand their replies, limited by what the animal has experienced and can understand. You gain 1 Boon to all rolls interacting with animals you are speaking with. This does not make an animal friendly or obedient, and does not compel it to act against its nature.</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Once on your turn, after resolving a Standard or Strong Main Action attack, move toward one creature affected by it: up to 1 square on Standard, or 2 on Strong. This movement does not provoke. You must be able to move and follow a legal route; it grants no attack.</t>
+          <t>For the scene, you can speak with animals. You can ask questions and understand their replies, limited by what the animal has experienced and can understand. You gain 1 Boon to all rolls interacting with animals you are speaking with. This does not make an animal friendly or obedient, and does not compel it to act against its nature.</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Move 1/2 toward a target after a Standard/Strong attack; good pursuit and a clean hunter identity.</t>
+          <t>Wildcaller: speak with animals for the scene; 1 Boon to all interactions with them.</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>Clarify whether the movement can be before the attack's other effects and whether it can follow a ranged attack (text says Main Action attack, any).</t>
+          <t>Approved: Maneuver. Speak with animals for the scene; 1 Boon to all rolls interacting with them.</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="79" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Read the Passing</t>
+          <t>Twin Strike</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>signature-warden-read-the-passing</t>
+          <t>signature-warden-follow-my-footsteps</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1321,46 +1358,54 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Accessible tracks or other physical signs you can examine for one minute.</t>
+          <t>One or two creatures within reach.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Examine the signs for one minute. Learn the direction of travel and one supported detail about the travelers, such as their number, gait or burden. If the signs cannot support either answer, learn what obscures them. Gain 1 Boon to your next roll following this trail this scene.</t>
+          <t>Requires two light melee weapons, one in each hand. Make one attack with each weapon. Each attack uses your normal attack procedure and deals 1 physical damage on Weak, 2 on Standard, 3 on Strong. You can target the same creature with both attacks or one creature with each. After the attacks, gain 1 Boon to defense until the start of your next turn.</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Examine the signs for one minute. Learn the direction of travel and one supported detail about the travelers, such as their number, gait or burden. If the signs cannot support either answer, learn what obscures them. Gain 1 Boon to your next roll following this trail this scene. Obvious tracks remain readable by anyone; this reveals no exact unseen location or evidence that does not exist.</t>
+          <t>Requires two light melee weapons, one in each hand. Make one attack with each weapon. Each attack uses your normal attack procedure and deals 1 physical damage on Weak, 2 on Standard, 3 on Strong. You can target the same creature with both attacks or one creature with each. After the attacks, gain 1 Boon to defense until the start of your next turn.</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>One-minute tracking analysis with direction, detail and a Boon; strong exploration.</t>
+          <t>Stalker: two light-weapon attacks, one or two targets, then 1 Boon to defense.</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether it can be used indoors or in urban terrain and whether the Boon applies to attack rolls or only tracking.</t>
+          <t>Approved: Main Action, Agility. Two light-weapon attacks (1/2/3 each); then 1 Boon to defense until your next turn.</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -1511,12 +1556,12 @@
     <row r="5" ht="91.5" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>A Watchful Rest</t>
+          <t>Volley</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>signature-warden-a-watchful-rest</t>
+          <t>signature-warden-stay-on-the-scent</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1526,164 +1571,188 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>A possible resting place and up to six willing companions; ten minutes of examination.</t>
+          <t>A 2x2 area within 10 squares.</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Spend ten minutes examining an accessible resting place. Learn its exposed approaches and any local environmental danger that observable signs can reveal. Prepare a watch plan. For the next eight hours while remaining there, you and the chosen companions gain 1 Boon to consequential rolls noticing approaching danger.</t>
+          <t>Requires a ranged weapon and ammunition. Make one Agility roll and apply it to each creature in the area. Weak: 1 physical damage. Standard: 2 physical damage. Strong: 3 physical damage. Roll once using the worst applicable Boon or Bane among the targets. Each target applies resistance separately. A creature can be affected once per use.</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Spend ten minutes examining an accessible resting place. Learn its exposed approaches and any local environmental danger that observable signs can reveal. Prepare a watch plan. For the next eight hours while remaining there, you and the chosen companions gain 1 Boon to consequential rolls noticing approaching danger. This grants no automatic detection, shelter, supplies, safe-place ruling or Grit recovery. Sleeping characters do not become awake observers.</t>
+          <t>Requires a ranged weapon and ammunition. Make one Agility roll and apply it to each creature in the area. Weak: 1 physical damage. Standard: 2 physical damage. Strong: 3 physical damage. Roll once using the worst applicable Boon or Bane among the targets. Each target applies resistance separately. A creature can be affected once per use.</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Ten-minute preparation grants 8 hours of party-wide Boon to notice danger; very strong exploration buff.</t>
+          <t>Marksman: 2x2 ranged area, one roll, 1/2/3 damage per target.</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Monitor; consider limiting to one watch or requiring the Warden to stay awake. Clarify whether it stacks with other watch or alertness bonuses.</t>
+          <t>Approved: Main Action, Agility. 2x2 area within 10: 1 / 2 / 3 physical damage to each creature.</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Power spike</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="79" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Stay on the Scent</t>
+          <t>Entangling Growth</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>signature-warden-stay-on-the-scent</t>
+          <t>signature-warden-through-bramble-and-stone</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>One visible enemy within 5 squares when it begins voluntary movement.</t>
+          <t>One or two creatures within 8 squares that are adjacent to each other.</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>After that movement ends, move up to 3 squares toward its final position without provoking, if you can still see it. Gain 1 Boon to your next attack against it before the end of your next turn. You must be able to move; this grants no attack and does not reveal a creature that becomes Hidden.</t>
+          <t>Make one Knowledge roll and apply it to each target. Weak: 2 physical damage, and the target is Slowed 1. Standard: 3 physical damage, and the target is Slowed 2. Strong: 5 physical damage, and the target is Slowed 2 and Grappled 1.</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>After that movement ends, move up to 3 squares toward its final position without provoking, if you can still see it. Gain 1 Boon to your next attack against it before the end of your next turn. You must be able to move; this grants no attack and does not reveal a creature that becomes Hidden.</t>
+          <t>Make one Knowledge roll and apply it to each target. Weak: 2 physical damage, and the target is Slowed 1. Standard: 3 physical damage, and the target is Slowed 2. Strong: 5 physical damage, and the target is Slowed 2 and Grappled 1.</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Reaction chase 3 and gain a Boon against a moving enemy; strong pursuit.</t>
+          <t>Wildcaller: one or two adjacent targets; damage plus Slowed and Grappled scaling.</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>Clarify whether it triggers on forced movement (text says voluntary, good) and whether the Boon applies to spells as well as attacks.</t>
+          <t>Approved: Main Action, Knowledge. 2 + Slowed 1 / 3 + Slowed 2 / 5 + Slowed 2 + Grappled 1 to one or two adjacent targets.</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="79" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Through Bramble and Stone</t>
+          <t>The Green Spear</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>signature-warden-through-bramble-and-stone</t>
+          <t>signature-warden-a-watchful-rest</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Self and one willing ally initially adjacent.</t>
+          <t>One creature within 8 squares.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Move up to 3 squares along a legal route, ignoring difficult-terrain surcharges and without provoking. Then the ally may move up to 1 square with the same benefits, ending adjacent to you. Both must be able to move and finish in supported free squares.</t>
+          <t>A spear of stone and living wood forms in your hand and flies at the target. Make a Knowledge attack roll. Weak: 3 physical damage. Standard: 5 physical damage, and the target is Slowed 1. Strong: 7 physical damage, and the target is Slowed 2 and Prone. The spear disappears after the attack. This does not require ammunition or a free hand after the throw.</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Move up to 3 squares along a legal route, ignoring difficult-terrain surcharges and without provoking. Then the ally may move up to 1 square with the same benefits, ending adjacent to you. Both must be able to move and finish in supported free squares. If the ally cannot reach a legal adjacent endpoint, it stays where it is. No gaps, barriers or occupied standing squares are crossed.</t>
+          <t>A spear of stone and living wood forms in your hand and flies at the target. Make a Knowledge attack roll. Weak: 3 physical damage. Standard: 5 physical damage, and the target is Slowed 1. Strong: 7 physical damage, and the target is Slowed 2 and Prone. The spear disappears after the attack. This does not require ammunition or a free hand after the throw.</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Self move 3 and ally move 1 ignoring difficult terrain; good group mobility.</t>
+          <t>Stalker: conjured spear thrown at range; damage plus Slowed and Prone.</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the ally can move if it is not adjacent at the end (text says must end adjacent).</t>
+          <t>Approved: Main Action, Knowledge. 3 / 5 + Slowed 1 / 7 + Slowed 2 + Prone at one target within 8 squares.</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -1834,71 +1903,79 @@
     <row r="5" ht="79" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Bring Them Through</t>
+          <t>Mark the Quarry</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>signature-warden-bring-them-through</t>
+          <t>signature-warden-turn-the-hunt</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Up to three willing allies visible within 4 squares, able to hear your directions and move.</t>
+          <t>One visible creature within 12 squares.</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Each ally may move up to 3 squares along a legal route without provoking, ignoring difficult-terrain surcharges. Resolve them one at a time; each ends in a supported free square. This does not cross gaps, barriers or occupied standing creatures. Allies spend no actions.</t>
+          <t>Requires a ranged weapon and ammunition. Make a Basic Ranged attack as part of this action. If it hits, the target is marked for one day with the glowing dust of a cave mushroom. While marked, you and each ally who can see it gain 2 Boons to any attack against it, ignore partial cover from it, and the target cannot hide. The mark deals no additional damage.</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Each ally may move up to 3 squares along a legal route without provoking, ignoring difficult-terrain surcharges. Resolve them one at a time; each ends in a supported free square. This does not cross gaps, barriers or occupied standing creatures. Allies spend no actions.</t>
+          <t>Requires a ranged weapon and ammunition. Make a Basic Ranged attack as part of this action. If it hits, the target is marked for one day with the glowing dust of a cave mushroom. While marked, you and each ally who can see it gain 2 Boons to any attack against it, ignore partial cover from it, and the target cannot hide. The mark deals no additional damage.</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Three allies move 3 ignoring difficult terrain; strong party mobility.</t>
+          <t>Marksman: Basic Ranged attack marks a quarry for a day; allies get 2 Boons, ignore partial cover, target cannot hide.</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether allies can move through each other's squares and whether the movement can be split around the Warden.</t>
+          <t>Approved: Main Action, Agility. Basic Ranged attack; on hit, mark for a day: allies get 2 Boons, ignore partial cover, target cannot hide.</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Know What You Hunt</t>
+          <t>Call the Wild</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>signature-warden-know-what-you-hunt</t>
+          <t>signature-warden-bring-them-through</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -1908,56 +1985,64 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>One visible creature within 8 squares that you have seen perform an ability or leave physical evidence.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Study the creature and name up to three willing allies within 5 squares who can hear you. The DA reveals two true, useful facts from its actual resistances, weaknesses or observed ability restrictions. If fewer exist, learn all that exist; invent none.</t>
+          <t>Call a real beast of CV 7 or lower that you are familiar with. It appears in a free square adjacent to you and uses its normal bestiary profile. It is controlled by the DA unless you spend a Maneuver to command it; when commanded, it follows your direction on your turn. It remains for the scene or until it drops to 0 HP. It is a living creature, not a spirit: it can be attacked, healed, and killed.</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Study the creature and name up to three willing allies within 5 squares who can hear you. The DA reveals two true, useful facts from its actual resistances, weaknesses or observed ability restrictions. If fewer exist, learn all that exist; invent none. Each chosen ally gains 1 Boon to its next roll acting against that creature this scene. This does not expose its thoughts, unseen location or an unobserved secret identity.</t>
+          <t>Call a real beast of CV 7 or lower that you are familiar with. It appears in a free square adjacent to you and uses its normal bestiary profile. It is controlled by the DA unless you spend a Maneuver to command it; when commanded, it follows your direction on your turn. It remains for the scene or until it drops to 0 HP. It is a living creature, not a spirit: it can be attacked, healed, and killed.</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Reveals two useful facts and grants three allies a Boon; strong Master support.</t>
+          <t>Wildcaller: call a real CV 7 or lower beast; DA controls it unless commanded with a Maneuver.</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>Overlaps with Intellect Expose the Mechanism. Differentiate by scope and duration; clarify whether 'observed ability restrictions' includes hidden weaknesses.</t>
+          <t>Approved: Main Action, Knowledge. Call a real beast of CV 7 or lower; DA controls it unless you spend a Maneuver to command.</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="129" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Turn the Hunt</t>
+          <t>Death from the Blind Spot</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>signature-warden-turn-the-hunt</t>
+          <t>signature-warden-know-what-you-hunt</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1967,50 +2052,54 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Knowledge</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>One visible creature: adjacent with a melee weapon, or within 8 squares with a ranged weapon and ammunition.</t>
+          <t>One creature you have hit or tracked this scene.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Choose melee or ranged before rolling Knowledge. Make one attack.</t>
+          <t>This ability consumes your Main Action and your movement for the turn. Move up to 6 squares to a square adjacent to the target, ignoring difficult terrain and without provoking. Then make one melee attack with 1 Boon. Weak: 6 physical damage. Standard: 9 physical damage, and the target is Prone. Strong: 12 physical damage, and the target is Prone and Dazed 1. If you cannot reach a square adjacent to the target, you cannot use this ability.</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Choose melee or ranged before rolling Knowledge. Make one attack.
-• Weak: Deal 4 physical damage and push the target 1 square.
-• Standard: Deal 5 physical damage and push it 2 squares.
-• Strong: Deal 7 physical damage, push it 3 squares and apply Slowed 2.
-After resolving the attack, you may move 1 square without provoking. Ranged use checks ammunition once after the attack. These are complete outcomes; this card requires no earlier signature.</t>
+          <t>This ability consumes your Main Action and your movement for the turn. Move up to 6 squares to a square adjacent to the target, ignoring difficult terrain and without provoking. Then make one melee attack with 1 Boon. Weak: 6 physical damage. Standard: 9 physical damage, and the target is Prone. Strong: 12 physical damage, and the target is Prone and Dazed 1. If you cannot reach a square adjacent to the target, you cannot use this ability.</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Knowledge-based melee or ranged attack with 4/5/7 damage, push and Slowed 2; strong capstone.</t>
+          <t>Stalker: full-turn 6-square close and melee strike against a quarry you have hit or tracked.</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the weapon grant applies to both modes or only the chosen one (text says choose one on learning) and whether ammunition is consumed on a miss.</t>
+          <t>Approved: Main Action + movement. Close 6 squares; 6 / 9 + Prone / 12 + Prone + Dazed 1 against a quarry you have hit or tracked.</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -2159,139 +2248,149 @@
       </c>
     </row>
     <row r="5" ht="79" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A5" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Follow My Footsteps</t>
+          <t>Steady Aim</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
+          <t>signature-warden-keep-the-quarry-close</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>None (no roll)</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Self; one visible creature.</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Aim at one visible creature. Until you move, you gain 1 Boon to all attacks you make against that creature and ignore partial cover from it.</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Marksman: aim once; all attacks against that creature gain 1 Boon and ignore partial cover until you move.</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Approved: Maneuver. Aim at one creature; until you move, all attacks against it gain 1 Boon and ignore partial cover.</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="79" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>signature-warden-read-the-passing</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>None (no roll)</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>For the scene, you can speak with animals. You can ask questions and understand their replies, limited by what the animal has experienced and can understand. You gain 1 Boon to all rolls interacting with animals you are speaking with. This does not make an animal friendly or obedient, and does not compel it to act against its nature.</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Wildcaller: speak with animals for the scene; 1 Boon to all interactions with them.</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Approved: Maneuver. Speak with animals for the scene; 1 Boon to all rolls interacting with them.</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="79" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
           <t>signature-warden-follow-my-footsteps</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Maneuver</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Self and one adjacent willing ally able to move.</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Move up to 1 square, then the ally may move up to 1 square. Both movements ignore difficult-terrain surcharges and do not provoke. Each must follow a legal route and end in a separate supported free square. This does not cross gaps or standing creatures. The ally spends no action.</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>Self and an ally move 1 ignoring difficult terrain; modest level-1 mobility.</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>Clarify whether the ally must remain adjacent throughout and whether it can move through the Warden's square.</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6" ht="79" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Keep the Quarry Close</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>signature-warden-keep-the-quarry-close</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Self, after your Main Action attack against one visible creature.</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Once on your turn, after resolving a Standard or Strong Main Action attack, move toward one creature affected by it: up to 1 square on Standard, or 2 on Strong. This movement does not provoke. You must be able to move and follow a legal route; it grants no attack.</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>Move 1/2 toward a target after a Standard/Strong attack; good pursuit and a clean hunter identity.</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Clarify whether the movement can be before the attack's other effects and whether it can follow a ranged attack (text says Main Action attack, any).</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="79" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Read the Passing</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>signature-warden-read-the-passing</t>
-        </is>
-      </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Main Action</t>
@@ -2299,395 +2398,439 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Accessible tracks or other physical signs you can examine for one minute.</t>
+          <t>One or two creatures within reach.</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Examine the signs for one minute. Learn the direction of travel and one supported detail about the travelers, such as their number, gait or burden. If the signs cannot support either answer, learn what obscures them. Gain 1 Boon to your next roll following this trail this scene.</t>
+          <t>Requires two light melee weapons, one in each hand. Make one attack with each weapon. Each attack uses your normal attack procedure and deals 1 physical damage on Weak, 2 on Standard, 3 on Strong. You can target the same creature with both attacks or one creature with each. After the attacks, gain 1 Boon to defense until the start of your next turn.</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>One-minute tracking analysis with direction, detail and a Boon; strong exploration.</t>
+          <t>Stalker: two light-weapon attacks, one or two targets, then 1 Boon to defense.</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether it can be used indoors or in urban terrain and whether the Boon applies to attack rolls or only tracking.</t>
+          <t>Approved: Main Action, Agility. Two light-weapon attacks (1/2/3 each); then 1 Boon to defense until your next turn.</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="91.5" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A8" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>A Watchful Rest</t>
+          <t>Volley</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>A 2x2 area within 10 squares.</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Requires a ranged weapon and ammunition. Make one Agility roll and apply it to each creature in the area. Weak: 1 physical damage. Standard: 2 physical damage. Strong: 3 physical damage. Roll once using the worst applicable Boon or Bane among the targets. Each target applies resistance separately. A creature can be affected once per use.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Marksman: 2x2 ranged area, one roll, 1/2/3 damage per target.</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Agility. 2x2 area within 10: 1 / 2 / 3 physical damage to each creature.</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="79" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>One or two creatures within 8 squares that are adjacent to each other.</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Make one Knowledge roll and apply it to each target. Weak: 2 physical damage, and the target is Slowed 1. Standard: 3 physical damage, and the target is Slowed 2. Strong: 5 physical damage, and the target is Slowed 2 and Grappled 1.</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Wildcaller: one or two adjacent targets; damage plus Slowed and Grappled scaling.</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Knowledge. 2 + Slowed 1 / 3 + Slowed 2 / 5 + Slowed 2 + Grappled 1 to one or two adjacent targets.</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="79" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
           <t>signature-warden-a-watchful-rest</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Main Action</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>A possible resting place and up to six willing companions; ten minutes of examination.</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Spend ten minutes examining an accessible resting place. Learn its exposed approaches and any local environmental danger that observable signs can reveal. Prepare a watch plan. For the next eight hours while remaining there, you and the chosen companions gain 1 Boon to consequential rolls noticing approaching danger.</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>Ten-minute preparation grants 8 hours of party-wide Boon to notice danger; very strong exploration buff.</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Monitor; consider limiting to one watch or requiring the Warden to stay awake. Clarify whether it stacks with other watch or alertness bonuses.</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>Power spike</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9" ht="79" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Stay on the Scent</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>signature-warden-stay-on-the-scent</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Reaction</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>One visible enemy within 5 squares when it begins voluntary movement.</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>After that movement ends, move up to 3 squares toward its final position without provoking, if you can still see it. Gain 1 Boon to your next attack against it before the end of your next turn. You must be able to move; this grants no attack and does not reveal a creature that becomes Hidden.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>Reaction chase 3 and gain a Boon against a moving enemy; strong pursuit.</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Clarify whether it triggers on forced movement (text says voluntary, good) and whether the Boon applies to spells as well as attacks.</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="79" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Through Bramble and Stone</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>signature-warden-through-bramble-and-stone</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Maneuver</t>
-        </is>
-      </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Self and one willing ally initially adjacent.</t>
+          <t>One creature within 8 squares.</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Move up to 3 squares along a legal route, ignoring difficult-terrain surcharges and without provoking. Then the ally may move up to 1 square with the same benefits, ending adjacent to you. Both must be able to move and finish in supported free squares.</t>
+          <t>A spear of stone and living wood forms in your hand and flies at the target. Make a Knowledge attack roll. Weak: 3 physical damage. Standard: 5 physical damage, and the target is Slowed 1. Strong: 7 physical damage, and the target is Slowed 2 and Prone. The spear disappears after the attack. This does not require ammunition or a free hand after the throw.</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Self move 3 and ally move 1 ignoring difficult terrain; good group mobility.</t>
+          <t>Stalker: conjured spear thrown at range; damage plus Slowed and Prone.</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>Clarify whether the ally can move if it is not adjacent at the end (text says must end adjacent).</t>
+          <t>Approved: Main Action, Knowledge. 3 / 5 + Slowed 1 / 7 + Slowed 2 + Prone at one target within 8 squares.</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="79" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A11" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Bring Them Through</t>
+          <t>Mark the Quarry</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
+          <t>signature-warden-turn-the-hunt</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>One visible creature within 12 squares.</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Requires a ranged weapon and ammunition. Make a Basic Ranged attack as part of this action. If it hits, the target is marked for one day with the glowing dust of a cave mushroom. While marked, you and each ally who can see it gain 2 Boons to any attack against it, ignore partial cover from it, and the target cannot hide. The mark deals no additional damage.</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Marksman: Basic Ranged attack marks a quarry for a day; allies get 2 Boons, ignore partial cover, target cannot hide.</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Agility. Basic Ranged attack; on hit, mark for a day: allies get 2 Boons, ignore partial cover, target cannot hide.</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="79" customHeight="1">
+      <c r="A12" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
           <t>signature-warden-bring-them-through</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Maneuver</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Up to three willing allies visible within 4 squares, able to hear your directions and move.</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Each ally may move up to 3 squares along a legal route without provoking, ignoring difficult-terrain surcharges. Resolve them one at a time; each ends in a supported free square. This does not cross gaps, barriers or occupied standing creatures. Allies spend no actions.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Three allies move 3 ignoring difficult terrain; strong party mobility.</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>Clarify whether allies can move through each other's squares and whether the movement can be split around the Warden.</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr"/>
-      <c r="M11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12" ht="79" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Know What You Hunt</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Call a real beast of CV 7 or lower that you are familiar with. It appears in a free square adjacent to you and uses its normal bestiary profile. It is controlled by the DA unless you spend a Maneuver to command it; when commanded, it follows your direction on your turn. It remains for the scene or until it drops to 0 HP. It is a living creature, not a spirit: it can be attacked, healed, and killed.</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Wildcaller: call a real CV 7 or lower beast; DA controls it unless commanded with a Maneuver.</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Knowledge. Call a real beast of CV 7 or lower; DA controls it unless you spend a Maneuver to command.</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66.5" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>signature-warden-know-what-you-hunt</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Main Action</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>One visible creature within 8 squares that you have seen perform an ability or leave physical evidence.</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Study the creature and name up to three willing allies within 5 squares who can hear you. The DA reveals two true, useful facts from its actual resistances, weaknesses or observed ability restrictions. If fewer exist, learn all that exist; invent none.</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>Reveals two useful facts and grants three allies a Boon; strong Master support.</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Overlaps with Intellect Expose the Mechanism. Differentiate by scope and duration; clarify whether 'observed ability restrictions' includes hidden weaknesses.</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="66.5" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Turn the Hunt</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>signature-warden-turn-the-hunt</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Main Action</t>
-        </is>
-      </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Knowledge</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>One visible creature: adjacent with a melee weapon, or within 8 squares with a ranged weapon and ammunition.</t>
+          <t>One creature you have hit or tracked this scene.</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Choose melee or ranged before rolling Knowledge. Make one attack.</t>
+          <t>This ability consumes your Main Action and your movement for the turn. Move up to 6 squares to a square adjacent to the target, ignoring difficult terrain and without provoking. Then make one melee attack with 1 Boon. Weak: 6 physical damage. Standard: 9 physical damage, and the target is Prone. Strong: 12 physical damage, and the target is Prone and Dazed 1. If you cannot reach a square adjacent to the target, you cannot use this ability.</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Knowledge-based melee or ranged attack with 4/5/7 damage, push and Slowed 2; strong capstone.</t>
+          <t>Stalker: full-turn 6-square close and melee strike against a quarry you have hit or tracked.</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the weapon grant applies to both modes or only the chosen one (text says choose one on learning) and whether ammunition is consumed on a miss.</t>
+          <t>Approved: Main Action + movement. Close 6 squares; 6 / 9 + Prone / 12 + Prone + Dazed 1 against a quarry you have hit or tracked.</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr"/>
-      <c r="M13" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M13"/>
@@ -2825,10 +2968,10 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0</v>
@@ -2861,13 +3004,13 @@
         <v>0</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0</v>
@@ -2894,13 +3037,13 @@
         <v>0</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>0</v>
@@ -2978,28 +3121,28 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
@@ -3009,16 +3152,16 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>0</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0</v>
@@ -3027,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
@@ -3040,28 +3183,28 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -3074,14 +3217,14 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>• A Watchful Rest is a very strong 8-hour buff for a 10-minute action; Know What You Hunt overlaps Intellect Expose the Mechanism. The class file lacks the standard 'Signature identity in play' section.</t>
+          <t>Levels 3 and 7 are almost all Main Actions. The Marksman and Stalker compete for the same slot; watch for a one-note turn.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>• Add the missing class section. Playtest A Watchful Rest; limit it to one watch or require the Warden to stay awake. Differentiate Know What You Hunt from the Intellect card by duration and scope.</t>
+          <t>The day-long mark and the DA-controlled beast are both campaign tools. Check that they do not solve exploration alone.</t>
         </is>
       </c>
     </row>
@@ -3221,41 +3364,17 @@
     <row r="5" ht="29" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>A Watchful Rest</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>signature-warden-a-watchful-rest</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Power spike</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>10-minute action grants 8 hours of party-wide Boon to notice danger.</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Limit to one watch or require the Warden to stay awake.</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
+          <t>No row-level flags for this class. Use the design questions below.</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
       <c r="J5" s="8" t="inlineStr"/>
     </row>
   </sheetData>
@@ -3304,7 +3423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3429,232 +3548,5880 @@
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="8" t="inlineStr"/>
-      <c r="B5" s="8" t="inlineStr"/>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>CHG-WAR-001</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>signature-warden-keep-the-quarry-close</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-keep-the-quarry-close.md</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Keep the Quarry Close</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>New title names the Marksman effect.</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="9" t="inlineStr"/>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr"/>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>CHG-WAR-002</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>signature-warden-keep-the-quarry-close</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-keep-the-quarry-close.md</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>You loose your shot, watch the quarry turn and run to keep its path in view.</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>You wait for the breath between heartbeats, and the arrow goes where you look.</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M6" s="9" t="inlineStr"/>
-      <c r="N6" s="9" t="inlineStr"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O6" s="9" t="inlineStr"/>
-      <c r="P6" s="9" t="inlineStr"/>
-      <c r="Q6" s="9" t="inlineStr"/>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="8" t="inlineStr"/>
-      <c r="B7" s="8" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>CHG-WAR-003</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>signature-warden-keep-the-quarry-close</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-keep-the-quarry-close.md</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M7" s="8" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O7" s="8" t="inlineStr"/>
-      <c r="P7" s="8" t="inlineStr"/>
-      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
-      <c r="J8" s="9" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr"/>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>CHG-WAR-004</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>signature-warden-keep-the-quarry-close</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-keep-the-quarry-close.md</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Self, after your Main Action attack against one visible creature.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Self; one visible creature.</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M8" s="9" t="inlineStr"/>
-      <c r="N8" s="9" t="inlineStr"/>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O8" s="9" t="inlineStr"/>
-      <c r="P8" s="9" t="inlineStr"/>
-      <c r="Q8" s="9" t="inlineStr"/>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="8" t="inlineStr"/>
-      <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>CHG-WAR-005</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>signature-warden-keep-the-quarry-close</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-keep-the-quarry-close.md</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Once on your turn, after resolving a Standard or Strong Main Action attack, move toward one creature affected by it: up to 1 square on Standard, or 2 on Strong. This movement does not provoke. You must be able to move and follow a legal route; it grants no attack.</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Aim at one visible creature. Until you move, you gain 1 Boon to all attacks you make against that creature and ignore partial cover from it.</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Marksman design.</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O9" s="8" t="inlineStr"/>
-      <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="9" t="inlineStr"/>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr"/>
-      <c r="I10" s="9" t="inlineStr"/>
-      <c r="J10" s="9" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="9" t="inlineStr"/>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>CHG-WAR-006</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>signature-warden-keep-the-quarry-close</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-keep-the-quarry-close.md</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Instant.</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Until you move.</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M10" s="9" t="inlineStr"/>
-      <c r="N10" s="9" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O10" s="9" t="inlineStr"/>
-      <c r="P10" s="9" t="inlineStr"/>
-      <c r="Q10" s="9" t="inlineStr"/>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="8" t="inlineStr"/>
-      <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>CHG-WAR-007</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>signature-warden-keep-the-quarry-close</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-keep-the-quarry-close.md</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Skill / Attack</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M11" s="8" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O11" s="8" t="inlineStr"/>
-      <c r="P11" s="8" t="inlineStr"/>
-      <c r="Q11" s="8" t="inlineStr"/>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="9" t="inlineStr"/>
-      <c r="B12" s="9" t="inlineStr"/>
-      <c r="C12" s="9" t="inlineStr"/>
-      <c r="D12" s="9" t="inlineStr"/>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr"/>
-      <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr"/>
-      <c r="J12" s="9" t="inlineStr"/>
-      <c r="K12" s="9" t="inlineStr"/>
-      <c r="L12" s="9" t="inlineStr"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>CHG-WAR-008</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>signature-warden-keep-the-quarry-close</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-keep-the-quarry-close.md</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Once on your turn.</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M12" s="9" t="inlineStr"/>
-      <c r="N12" s="9" t="inlineStr"/>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O12" s="9" t="inlineStr"/>
-      <c r="P12" s="9" t="inlineStr"/>
-      <c r="Q12" s="9" t="inlineStr"/>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
-      <c r="B13" s="8" t="inlineStr"/>
-      <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr"/>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>CHG-WAR-009</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>signature-warden-read-the-passing</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-read-the-passing.md</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Read the Passing</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>New title names the Wildcaller effect.</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M13" s="8" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O13" s="8" t="inlineStr"/>
-      <c r="P13" s="8" t="inlineStr"/>
-      <c r="Q13" s="8" t="inlineStr"/>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="9" t="inlineStr"/>
-      <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="9" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr"/>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="9" t="inlineStr"/>
-      <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr"/>
-      <c r="I14" s="9" t="inlineStr"/>
-      <c r="J14" s="9" t="inlineStr"/>
-      <c r="K14" s="9" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>CHG-WAR-010</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>signature-warden-read-the-passing</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-read-the-passing.md</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>You kneel beside a bent stem, brush grit from a footprint and look toward the gap the travelers chose.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>You make a sound somewhere between a bird and a question, and the forest answers.</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M14" s="9" t="inlineStr"/>
-      <c r="N14" s="9" t="inlineStr"/>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O14" s="9" t="inlineStr"/>
-      <c r="P14" s="9" t="inlineStr"/>
-      <c r="Q14" s="9" t="inlineStr"/>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
-      <c r="B15" s="8" t="inlineStr"/>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>CHG-WAR-011</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>signature-warden-read-the-passing</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-read-the-passing.md</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M15" s="8" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O15" s="8" t="inlineStr"/>
-      <c r="P15" s="8" t="inlineStr"/>
-      <c r="Q15" s="8" t="inlineStr"/>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="9" t="inlineStr"/>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="9" t="inlineStr"/>
-      <c r="D16" s="9" t="inlineStr"/>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="9" t="inlineStr"/>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr"/>
-      <c r="J16" s="9" t="inlineStr"/>
-      <c r="K16" s="9" t="inlineStr"/>
-      <c r="L16" s="9" t="inlineStr"/>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>CHG-WAR-012</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>signature-warden-read-the-passing</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-read-the-passing.md</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Accessible tracks or other physical signs you can examine for one minute.</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M16" s="9" t="inlineStr"/>
-      <c r="N16" s="9" t="inlineStr"/>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O16" s="9" t="inlineStr"/>
-      <c r="P16" s="9" t="inlineStr"/>
-      <c r="Q16" s="9" t="inlineStr"/>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CHG-WAR-013</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>signature-warden-read-the-passing</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-read-the-passing.md</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Examine the signs for one minute. Learn the direction of travel and one supported detail about the travelers, such as their number, gait or burden. If the signs cannot support either answer, learn what obscures them. Gain 1 Boon to your next roll following this trail this scene. Obvious tracks remain readable by anyone; this reveals no exact unseen location or evidence that does not exist.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>For the scene, you can speak with animals. You can ask questions and understand their replies, limited by what the animal has experienced and can understand. You gain 1 Boon to all rolls interacting with animals you are speaking with. This does not make an animal friendly or obedient, and does not compel it to act against its nature.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Wildcaller design.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CHG-WAR-014</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>signature-warden-read-the-passing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-read-the-passing.md</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Information remains known; the Boon ends when used or the scene ends.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>The scene.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CHG-WAR-015</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>signature-warden-read-the-passing</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-read-the-passing.md</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Skill / Utility</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Skill / Utility / Support</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CHG-WAR-016</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>signature-warden-read-the-passing</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Beast Speech</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-read-the-passing.md</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Once per set of signs; new evidence permits another use.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHG-WAR-017</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>signature-warden-follow-my-footsteps</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-follow-my-footsteps.md</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Follow My Footsteps</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>New title names the Stalker effect.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHG-WAR-018</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>signature-warden-follow-my-footsteps</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-follow-my-footsteps.md</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>You test the ground with your boot and offer a hand, bringing your companion onto the firm patch beside you.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Two blades, one motion.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CHG-WAR-019</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>signature-warden-follow-my-footsteps</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-follow-my-footsteps.md</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CHG-WAR-020</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>signature-warden-follow-my-footsteps</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-follow-my-footsteps.md</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CHG-WAR-021</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>signature-warden-follow-my-footsteps</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-follow-my-footsteps.md</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Self and one adjacent willing ally able to move.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>One or two creatures within reach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CHG-WAR-022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>signature-warden-follow-my-footsteps</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-follow-my-footsteps.md</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Move up to 1 square, then the ally may move up to 1 square. Both movements ignore difficult-terrain surcharges and do not provoke. Each must follow a legal route and end in a separate supported free square. This does not cross gaps or standing creatures. The ally spends no action.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Requires two light melee weapons, one in each hand. Make one attack with each weapon. Each attack uses your normal attack procedure and deals 1 physical damage on Weak, 2 on Standard, 3 on Strong. You can target the same creature with both attacks or one creature with each. After the attacks, gain 1 Boon to defense until the start of your next turn.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Stalker design.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CHG-WAR-023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>signature-warden-follow-my-footsteps</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-follow-my-footsteps.md</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Instant.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Immediate; the defense Boon lasts until the start of your next turn.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CHG-WAR-024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>signature-warden-follow-my-footsteps</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-follow-my-footsteps.md</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Defense</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CHG-WAR-025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>signature-warden-follow-my-footsteps</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Twin Strike</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-follow-my-footsteps.md</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Each participant moves once per use.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CHG-WAR-026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-stay-on-the-scent.md</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Stay on the Scent</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>New title names the Marksman effect.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CHG-WAR-027</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-stay-on-the-scent.md</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>You watch the first turn of their shoulders and cut toward their escape route before their footsteps fade.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>You empty the quiver into the space where the enemy is standing.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CHG-WAR-028</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-stay-on-the-scent.md</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Reaction</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHG-WAR-029</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-stay-on-the-scent.md</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CHG-WAR-030</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-stay-on-the-scent.md</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>One visible enemy within 5 squares when it begins voluntary movement.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>A 2x2 area within 10 squares.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHG-WAR-031</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-stay-on-the-scent.md</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>After that movement ends, move up to 3 squares toward its final position without provoking, if you can still see it. Gain 1 Boon to your next attack against it before the end of your next turn. You must be able to move; this grants no attack and does not reveal a creature that becomes Hidden.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Requires a ranged weapon and ammunition. Make one Agility roll and apply it to each creature in the area. Weak: 1 physical damage. Standard: 2 physical damage. Strong: 3 physical damage. Roll once using the worst applicable Boon or Bane among the targets. Each target applies resistance separately. A creature can be affected once per use.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Marksman design.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CHG-WAR-032</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-stay-on-the-scent.md</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Movement is immediate; the Boon ends when used or at the end of your next turn.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Immediate.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CHG-WAR-033</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-stay-on-the-scent.md</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Skill / Attack</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CHG-WAR-034</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>signature-warden-stay-on-the-scent</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-stay-on-the-scent.md</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>One Reaction per use; repeated uses do not multiply the unused Boon.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHG-WAR-035</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-through-bramble-and-stone.md</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Through Bramble and Stone</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>New title names the Wildcaller effect.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CHG-WAR-036</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-through-bramble-and-stone.md</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>You lift a thorny branch, find a foothold between the stones and turn to show your companion the way through.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>You speak to the roots, and they remember they were here first.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CHG-WAR-037</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-through-bramble-and-stone.md</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CHG-WAR-038</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-through-bramble-and-stone.md</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CHG-WAR-039</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-through-bramble-and-stone.md</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Self and one willing ally initially adjacent.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>One or two creatures within 8 squares that are adjacent to each other.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CHG-WAR-040</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-through-bramble-and-stone.md</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Move up to 3 squares along a legal route, ignoring difficult-terrain surcharges and without provoking. Then the ally may move up to 1 square with the same benefits, ending adjacent to you. Both must be able to move and finish in supported free squares. If the ally cannot reach a legal adjacent endpoint, it stays where it is. No gaps, barriers or occupied standing squares are crossed.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Make one Knowledge roll and apply it to each target. Weak: 2 physical damage, and the target is Slowed 1. Standard: 3 physical damage, and the target is Slowed 2. Strong: 5 physical damage, and the target is Slowed 2 and Grappled 1.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Wildcaller design.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHG-WAR-041</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-through-bramble-and-stone.md</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Instant.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Immediate; Slowed and Grappled use their normal rules.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CHG-WAR-042</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-through-bramble-and-stone.md</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Magic / Attack / Control</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHG-WAR-043</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>signature-warden-through-bramble-and-stone</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Entangling Growth</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-through-bramble-and-stone.md</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Each participant moves once per use.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CHG-WAR-044</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>signature-warden-a-watchful-rest</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-a-watchful-rest.md</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>A Watchful Rest</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>New title names the Stalker effect.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CHG-WAR-045</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>signature-warden-a-watchful-rest</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-a-watchful-rest.md</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>You circle the camp, test the ground for water and point out the approaches before assigning the first watch.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>You ask the wood for a weapon, and it gives you a spear. You throw it before the answer stops moving.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CHG-WAR-046</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>signature-warden-a-watchful-rest</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-a-watchful-rest.md</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CHG-WAR-047</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>signature-warden-a-watchful-rest</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-a-watchful-rest.md</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>A possible resting place and up to six willing companions; ten minutes of examination.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>One creature within 8 squares.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CHG-WAR-048</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>signature-warden-a-watchful-rest</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-a-watchful-rest.md</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Spend ten minutes examining an accessible resting place. Learn its exposed approaches and any local environmental danger that observable signs can reveal. Prepare a watch plan. For the next eight hours while remaining there, you and the chosen companions gain 1 Boon to consequential rolls noticing approaching danger. This grants no automatic detection, shelter, supplies, safe-place ruling or Grit recovery. Sleeping characters do not become awake observers.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>A spear of stone and living wood forms in your hand and flies at the target. Make a Knowledge attack roll. Weak: 3 physical damage. Standard: 5 physical damage, and the target is Slowed 1. Strong: 7 physical damage, and the target is Slowed 2 and Prone. The spear disappears after the attack. This does not require ammunition or a free hand after the throw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Stalker design.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CHG-WAR-049</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>signature-warden-a-watchful-rest</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-a-watchful-rest.md</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Eight hours or until the group leaves.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Immediate; Slowed and Prone use their normal rules.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CHG-WAR-050</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>signature-warden-a-watchful-rest</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-a-watchful-rest.md</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Skill / Utility</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Magic / Attack / Control</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CHG-WAR-051</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>signature-warden-a-watchful-rest</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>The Green Spear</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-a-watchful-rest.md</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>One prepared resting place per Warden; preparing another ends the previous benefit.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CHG-WAR-052</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>signature-warden-bring-them-through</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-bring-them-through.md</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bring Them Through</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>New title names the Wildcaller effect.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CHG-WAR-053</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>signature-warden-bring-them-through</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-bring-them-through.md</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>You call out footholds and openings in a steady voice, guiding your companions through the broken ground before the enemy can close it.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>You call, and something with teeth and hunger answers. It is not yours. It is here for the hunt.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CHG-WAR-054</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>signature-warden-bring-them-through</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-bring-them-through.md</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CHG-WAR-055</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>signature-warden-bring-them-through</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-bring-them-through.md</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHG-WAR-056</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>signature-warden-bring-them-through</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-bring-them-through.md</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Up to three willing allies visible within 4 squares, able to hear your directions and move.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHG-WAR-057</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>signature-warden-bring-them-through</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-bring-them-through.md</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Each ally may move up to 3 squares along a legal route without provoking, ignoring difficult-terrain surcharges. Resolve them one at a time; each ends in a supported free square. This does not cross gaps, barriers or occupied standing creatures. Allies spend no actions.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Call a real beast of CV 7 or lower that you are familiar with. It appears in a free square adjacent to you and uses its normal bestiary profile. It is controlled by the DA unless you spend a Maneuver to command it; when commanded, it follows your direction on your turn. It remains for the scene or until it drops to 0 HP. It is a living creature, not a spirit: it can be attacked, healed, and killed.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Wildcaller design.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CHG-WAR-058</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>signature-warden-bring-them-through</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-bring-them-through.md</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Instant.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>The scene, or until the beast drops.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CHG-WAR-059</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>signature-warden-bring-them-through</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-bring-them-through.md</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Magic / Support / Utility</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CHG-WAR-060</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>signature-warden-bring-them-through</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Call the Wild</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-bring-them-through.md</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Each ally moves once per use.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CHG-WAR-061</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>signature-warden-know-what-you-hunt</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-know-what-you-hunt.md</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Know What You Hunt</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>New title names the Stalker effect.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CHG-WAR-062</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>signature-warden-know-what-you-hunt</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-know-what-you-hunt.md</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>You point out the plates that overlap, the limb it favors and the moment its breath catches, telling your companions where to meet it.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>You have run it to ground. It turns, and you are already in the one place it cannot see.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CHG-WAR-063</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>signature-warden-know-what-you-hunt</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-know-what-you-hunt.md</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CHG-WAR-064</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>signature-warden-know-what-you-hunt</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-know-what-you-hunt.md</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>One visible creature within 8 squares that you have seen perform an ability or leave physical evidence.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>One creature you have hit or tracked this scene.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CHG-WAR-065</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>signature-warden-know-what-you-hunt</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-know-what-you-hunt.md</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Study the creature and name up to three willing allies within 5 squares who can hear you. The DA reveals two true, useful facts from its actual resistances, weaknesses or observed ability restrictions. If fewer exist, learn all that exist; invent none. Each chosen ally gains 1 Boon to its next roll acting against that creature this scene. This does not expose its thoughts, unseen location or an unobserved secret identity.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>This ability consumes your Main Action and your movement for the turn. Move up to 6 squares to a square adjacent to the target, ignoring difficult terrain and without provoking. Then make one melee attack with 1 Boon. Weak: 6 physical damage. Standard: 9 physical damage, and the target is Prone. Strong: 12 physical damage, and the target is Prone and Dazed 1. If you cannot reach a square adjacent to the target, you cannot use this ability.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Stalker design.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CHG-WAR-066</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>signature-warden-know-what-you-hunt</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-know-what-you-hunt.md</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Facts remain known; each Boon ends when used or the scene ends.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Immediate; Prone and Dazed use their normal rules.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CHG-WAR-067</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>signature-warden-know-what-you-hunt</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-know-what-you-hunt.md</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Skill / Utility</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Movement / Control</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CHG-WAR-068</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>signature-warden-know-what-you-hunt</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Death from the Blind Spot</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-know-what-you-hunt.md</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Once per creature per scene; repeated uses do not renew spent benefits.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CHG-WAR-069</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>signature-warden-turn-the-hunt</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Mark the Quarry</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-turn-the-hunt.md</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Turn the Hunt</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Mark the Quarry</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>New title names the Marksman effect.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CHG-WAR-070</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>signature-warden-turn-the-hunt</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mark the Quarry</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-turn-the-hunt.md</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>You read the turn of the beast’s weight and strike where its next step must fall, driving it toward the ground you chose.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>You put an arrow through its shoulder and point. The rest of the party follows the mark.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CHG-WAR-071</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>signature-warden-turn-the-hunt</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Mark the Quarry</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-turn-the-hunt.md</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CHG-WAR-072</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>signature-warden-turn-the-hunt</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mark the Quarry</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-turn-the-hunt.md</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>One visible creature: adjacent with a melee weapon, or within 8 squares with a ranged weapon and ammunition.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>One visible creature within 12 squares.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CHG-WAR-073</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>signature-warden-turn-the-hunt</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mark the Quarry</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-turn-the-hunt.md</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Choose melee or ranged before rolling Knowledge. Make one attack. - **Weak:** Deal 4 physical damage and push the target 1 square. - **Standard:** Deal 5 physical damage and push it 2 squares. - **Strong:** Deal 7 physical damage, push it 3 squares and apply Slowed 2. After resolving the attack, you may move 1 square without provoking. Ranged use checks ammunition once after the attack. These are complete outcomes; this card requires no earlier signature.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Requires a ranged weapon and ammunition. Make a Basic Ranged attack as part of this action. If it hits, the target is marked for one day with the glowing dust of a cave mushroom. While marked, you and each ally who can see it gain 2 Boons to any attack against it, ignore partial cover from it, and the target cannot hide. The mark deals no additional damage.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Marksman design.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CHG-WAR-074</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>signature-warden-turn-the-hunt</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mark the Quarry</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-turn-the-hunt.md</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Damage and movement are immediate; Slowed decays normally.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>One day.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CHG-WAR-075</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>signature-warden-turn-the-hunt</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Mark the Quarry</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-turn-the-hunt.md</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Movement</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Support</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CHG-WAR-076</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CLS-10</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>signature-warden-turn-the-hunt</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Mark the Quarry</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>design/cards/signature-warden-turn-the-hunt.md</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>One attack per use.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Once per day.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q204"/>
